--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342808</v>
+        <v>121342650</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508361</v>
+        <v>508374</v>
       </c>
       <c r="R2" t="n">
-        <v>6956640</v>
+        <v>6956641</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342650</v>
+        <v>121342814</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R3" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342814</v>
+        <v>121342686</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,31 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R4" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342686</v>
+        <v>121342808</v>
       </c>
       <c r="B5" t="n">
-        <v>57369</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1046,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R5" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1124,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342650</v>
+        <v>121342686</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342686</v>
+        <v>121342650</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R3" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342650</v>
+        <v>121342808</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R4" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342808</v>
+        <v>121342814</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,16 +1055,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508361</v>
+        <v>508367</v>
       </c>
       <c r="R5" t="n">
-        <v>6956640</v>
+        <v>6956629</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342686</v>
+        <v>121342808</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R2" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342650</v>
+        <v>121342814</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R3" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342808</v>
+        <v>121342686</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,31 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508361</v>
+        <v>508374</v>
       </c>
       <c r="R4" t="n">
-        <v>6956640</v>
+        <v>6956641</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,31 +1047,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R5" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342808</v>
+        <v>121342686</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508361</v>
+        <v>508374</v>
       </c>
       <c r="R2" t="n">
-        <v>6956640</v>
+        <v>6956641</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R3" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342686</v>
+        <v>121342814</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R4" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342650</v>
+        <v>121342808</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1046,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R5" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1124,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342686</v>
+        <v>121342808</v>
       </c>
       <c r="B2" t="n">
-        <v>57375</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R2" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342650</v>
+        <v>121342814</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R3" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,31 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R4" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342808</v>
+        <v>121342686</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,31 +1047,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508361</v>
+        <v>508374</v>
       </c>
       <c r="R5" t="n">
-        <v>6956640</v>
+        <v>6956641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121342808</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121342814</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342650</v>
+        <v>121342686</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>57376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342686</v>
+        <v>121342650</v>
       </c>
       <c r="B5" t="n">
-        <v>57375</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1047,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121342808</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +809,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R3" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +921,7 @@
         <v>121342686</v>
       </c>
       <c r="B4" t="n">
-        <v>57376</v>
+        <v>57377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1035,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342650</v>
+        <v>121342814</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1051,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R5" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342808</v>
+        <v>121342650</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508361</v>
+        <v>508374</v>
       </c>
       <c r="R2" t="n">
-        <v>6956640</v>
+        <v>6956641</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342650</v>
+        <v>121342814</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R3" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342686</v>
+        <v>121342808</v>
       </c>
       <c r="B4" t="n">
-        <v>57377</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,35 +925,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -967,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R4" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342814</v>
+        <v>121342686</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,31 +1047,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R5" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342650</v>
+        <v>121342814</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R2" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342814</v>
+        <v>121342686</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R3" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342808</v>
+        <v>121342650</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508361</v>
+        <v>508374</v>
       </c>
       <c r="R4" t="n">
-        <v>6956640</v>
+        <v>6956641</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barkskalade granar</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121342686</v>
+        <v>121342808</v>
       </c>
       <c r="B5" t="n">
-        <v>57377</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1046,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508374</v>
+        <v>508361</v>
       </c>
       <c r="R5" t="n">
-        <v>6956641</v>
+        <v>6956640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1124,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barkskalade granar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R2" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342686</v>
+        <v>121342814</v>
       </c>
       <c r="B3" t="n">
-        <v>57377</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R3" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342650</v>
+        <v>121342686</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>57377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50587-2019 artfynd.xlsx
+++ b/artfynd/A 50587-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121342650</v>
+        <v>121342686</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>57378</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121342814</v>
+        <v>121342650</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508367</v>
+        <v>508374</v>
       </c>
       <c r="R3" t="n">
-        <v>6956629</v>
+        <v>6956641</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121342686</v>
+        <v>121342814</v>
       </c>
       <c r="B4" t="n">
-        <v>57377</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508374</v>
+        <v>508367</v>
       </c>
       <c r="R4" t="n">
-        <v>6956641</v>
+        <v>6956629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1037,7 @@
         <v>121342808</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
